--- a/results/Int Task Remove ACC -0.5/Rando_8_permute.xlsx
+++ b/results/Int Task Remove ACC -0.5/Rando_8_permute.xlsx
@@ -440,887 +440,887 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.7619922055408987</v>
+        <v>0.7581712914634224</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.7595204541284695</v>
+        <v>0.7659748451547188</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.7611748786860768</v>
+        <v>0.7771857067840897</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.7437389678668362</v>
+        <v>0.7847318440348979</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.7535753601457664</v>
+        <v>0.7792256628769905</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.7480339868784837</v>
+        <v>0.7818563719070486</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.7502004763983525</v>
+        <v>0.7932768045248353</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.7368385465105244</v>
+        <v>0.7875060894211728</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.7274284137136928</v>
+        <v>0.7858390115208685</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.7294739056440236</v>
+        <v>0.7858390115208685</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.7248483180544221</v>
+        <v>0.7893194715964089</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.7285442803727675</v>
+        <v>0.7888074066341476</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.7380402186497618</v>
+        <v>0.7912060059091111</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.7467595580187396</v>
+        <v>0.7877733912856428</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.7461996476044059</v>
+        <v>0.7834629510125837</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.7490118530187713</v>
+        <v>0.7834629510125837</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.7436673973972074</v>
+        <v>0.7810010850241362</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7439473526043743</v>
+        <v>0.7810010850241362</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7364996741764256</v>
+        <v>0.7769761357956738</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.7384593606265935</v>
+        <v>0.7701615199195248</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7374731907301612</v>
+        <v>0.7669637829698661</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7436575119732255</v>
+        <v>0.76157148189623</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7391276152877686</v>
+        <v>0.7631780610017651</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.737286158508424</v>
+        <v>0.7666612889960205</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7121506886581763</v>
+        <v>0.7767044843446518</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7187541518780725</v>
+        <v>0.7741595807947566</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.7077655145798141</v>
+        <v>0.7740259298625214</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7027516275362045</v>
+        <v>0.7670242817646351</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.6896949595409367</v>
+        <v>0.735172654861098</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.6778257286743725</v>
+        <v>0.7085318326468895</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.6130678978369111</v>
+        <v>0.7238154889567951</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.6109239470837209</v>
+        <v>0.6300656866652747</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.5916058515383301</v>
+        <v>0.6268651817969012</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.6380598313309418</v>
+        <v>0.6664697490209476</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.6269023509910731</v>
+        <v>0.6674938789454704</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.6081635412910206</v>
+        <v>0.6680537893598042</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.5790636210070795</v>
+        <v>0.6511398289268068</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.5949605690208211</v>
+        <v>0.6248916557531586</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.6009127805087908</v>
+        <v>0.600625707796357</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.6016300668729161</v>
+        <v>0.6311985562535982</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.5800300200555482</v>
+        <v>0.6279391342582927</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.5805828129646149</v>
+        <v>0.6140975635988637</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.5477268269845187</v>
+        <v>0.5177929723334662</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.5671702697059996</v>
+        <v>0.5447627814577916</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.5649432813913615</v>
+        <v>0.4722421248758391</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.5363277468825327</v>
+        <v>0.4715584489532523</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.5317274659783249</v>
+        <v>0.4448037466547725</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.5900139028602881</v>
+        <v>0.4087587228981216</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.6077803822574829</v>
+        <v>0.3910780489810896</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.6079871853271839</v>
+        <v>0.3900792257419604</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.6161185396777193</v>
+        <v>0.3883994944989593</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.5842162994033949</v>
+        <v>0.3640236206274793</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.5623248302870412</v>
+        <v>0.3786445581136397</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.5957308412574892</v>
+        <v>0.3949199201574076</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.5980084429429144</v>
+        <v>0.391590113943351</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.5957688012855796</v>
+        <v>0.4219798843484478</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.5730797761623677</v>
+        <v>0.4376941497270042</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.5652789903897862</v>
+        <v>0.4162261721740341</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.5327464554823771</v>
+        <v>0.4203677694054827</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.5385397093527182</v>
+        <v>0.4251523146127129</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.5310540708966791</v>
+        <v>0.4681626081069966</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.5251777794648902</v>
+        <v>0.4724758162987707</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.5249583230524923</v>
+        <v>0.4697367630218713</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.5018825801431093</v>
+        <v>0.4935665660725922</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.5018825801431093</v>
+        <v>0.4907614781634938</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.519515408608069</v>
+        <v>0.489333627523551</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.519515408608069</v>
+        <v>0.4904799412884899</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.5076714844268985</v>
+        <v>0.4812323248619204</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.5078656341539026</v>
+        <v>0.4721401073003461</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.5018908838992541</v>
+        <v>0.446748407260488</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.4970584932399517</v>
+        <v>0.4471015146051208</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.4994444391722184</v>
+        <v>0.4548671082683268</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.4909038282688329</v>
+        <v>0.4576033936265113</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.4906420622417927</v>
+        <v>0.4576033936265113</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.4900469597180835</v>
+        <v>0.4569323710466212</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.4900469597180835</v>
+        <v>0.4547828844560011</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.4900469597180835</v>
+        <v>0.452762699211064</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.4897670045109166</v>
+        <v>0.4443909313492892</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.4804399092755329</v>
+        <v>0.4577781679225109</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.4814007724865716</v>
+        <v>0.486455782893946</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.4814007724865716</v>
+        <v>0.4789701444379069</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.4811813160741739</v>
+        <v>0.4795174015095438</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.4880619665825219</v>
+        <v>0.4846396327999949</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.4844253168080678</v>
+        <v>0.4846396327999949</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.4903676428720557</v>
+        <v>0.4846396327999949</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.4903676428720557</v>
+        <v>0.481672819354553</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.4975480194355344</v>
+        <v>0.4722753399004182</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.4971217599534357</v>
+        <v>0.4805585343633154</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4971217599534357</v>
+        <v>0.4836060128684495</v>
       </c>
     </row>
   </sheetData>
